--- a/PRACTICAS APLICADAS/cronograma excel.xlsx
+++ b/PRACTICAS APLICADAS/cronograma excel.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Practicas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\PRACTICAS APLICADAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9FB2F7-5381-4E6A-A230-DD1D110E6CE1}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649E1D8E-F9A8-4D27-9FE7-C982576C0B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{693F3BED-ABCA-4C35-84F7-5735A91B3CFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1 (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId3"/>
-    <sheet name="Hoja4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="179021"/>
   <extLst>
@@ -28,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>Actividades</t>
   </si>
@@ -105,178 +103,7 @@
     <t>No.</t>
   </si>
   <si>
-    <t>Introducción al curso y diagnóstico</t>
-  </si>
-  <si>
-    <t>Unidad 1: Ecuaciones y desigualdades</t>
-  </si>
-  <si>
-    <t>Unidad 2: Geometría</t>
-  </si>
-  <si>
-    <t>Unidad 3: Gráficas y funciones</t>
-  </si>
-  <si>
-    <t>Unidad 4: Funciones polinomiales y racionales</t>
-  </si>
-  <si>
-    <t>Unidad 5: Funciones exponenciales y logarítmicas</t>
-  </si>
-  <si>
-    <t>Semana</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Unidad / Tema</t>
-  </si>
-  <si>
-    <t>Actividades del Laboratorio</t>
-  </si>
-  <si>
-    <t>Producto / Evaluación</t>
-  </si>
-  <si>
-    <t>Ponderación</t>
-  </si>
-  <si>
-    <t>11-15 agosto</t>
-  </si>
-  <si>
-    <t>Prueba diagnóstica, hoja de repaso, dinámicas grupales</t>
-  </si>
-  <si>
-    <t>Lista de cotejo</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>18-29 agosto</t>
-  </si>
-  <si>
-    <t>Resolución de ecuaciones, uso de números complejos, modelado</t>
-  </si>
-  <si>
-    <t>Hoja de trabajo</t>
-  </si>
-  <si>
-    <t>1-12 septiembre</t>
-  </si>
-  <si>
-    <t>Construcción de modelos geométricos, cálculo de áreas y volúmenes</t>
-  </si>
-  <si>
-    <t>Modelos + ejercicios</t>
-  </si>
-  <si>
-    <t>15-19 septiembre</t>
-  </si>
-  <si>
-    <t>Graficación con software, funciones lineales, transformaciones</t>
-  </si>
-  <si>
-    <t>Hoja + lectura</t>
-  </si>
-  <si>
-    <t>22 sept - 3 octubre</t>
-  </si>
-  <si>
-    <t>División de polinomios, ceros, modelos aplicados</t>
-  </si>
-  <si>
-    <t>Ejercicios + modelo</t>
-  </si>
-  <si>
-    <t>6-10 octubre</t>
-  </si>
-  <si>
-    <t>Leyes de logaritmos, modelado de crecimiento o decaimiento</t>
-  </si>
-  <si>
-    <t>13-17 octubre</t>
-  </si>
-  <si>
-    <t>Proyecto intermedio</t>
-  </si>
-  <si>
-    <t>Desarrollo de un caso aplicado con funciones</t>
-  </si>
-  <si>
-    <t>Informe + presentación</t>
-  </si>
-  <si>
-    <t>20-31 octubre</t>
-  </si>
-  <si>
-    <t>Unidad 6: Trigonometría</t>
-  </si>
-  <si>
-    <t>Gráficas trigonométricas, ley de senos y cosenos</t>
-  </si>
-  <si>
-    <t>Hoja + discusión</t>
-  </si>
-  <si>
-    <t>3-7 noviembre</t>
-  </si>
-  <si>
-    <t>Unidad 7: Geometría Analítica</t>
-  </si>
-  <si>
-    <t>Parábola, elipse, hipérbola con graficación y análisis</t>
-  </si>
-  <si>
-    <t>10-14 noviembre</t>
-  </si>
-  <si>
-    <t>Presentación de proyecto final</t>
-  </si>
-  <si>
-    <t>Proyecto integrador con aplicación real</t>
-  </si>
-  <si>
-    <t>Exposición + entrega escrita</t>
-  </si>
-  <si>
-    <t>Total acumulado en todo el curso</t>
-  </si>
-  <si>
-    <t>100% (20 pts)</t>
-  </si>
-  <si>
-    <t>Claro, aquí tienes el texto en tercera persona y en forma concisa:</t>
-  </si>
-  <si>
-    <t>El curso inicia con una prueba diagnóstica, hoja de repaso y dinámicas grupales, evaluadas mediante una lista de cotejo.</t>
-  </si>
-  <si>
-    <t>Se trabaja la resolución de ecuaciones y desigualdades, el uso de números complejos y el modelado, con una hoja de trabajo como evidencia.</t>
-  </si>
-  <si>
-    <t>Se desarrolla la construcción de modelos geométricos y el cálculo de áreas y volúmenes, evaluados con ejercicios y modelos elaborados por los estudiantes.</t>
-  </si>
-  <si>
-    <t>Se aplica software para graficar funciones lineales y sus transformaciones, con hoja de trabajo y lectura como evidencias.</t>
-  </si>
-  <si>
-    <t>Se estudia la división de polinomios, la identificación de ceros y la aplicación de modelos, evaluados mediante ejercicios y un modelo contextual.</t>
-  </si>
-  <si>
-    <t>Se modelan fenómenos de crecimiento y decaimiento con funciones exponenciales y logarítmicas, utilizando una hoja de trabajo.</t>
-  </si>
-  <si>
-    <t>El proyecto intermedio consiste en la resolución de un caso aplicado con funciones, con entrega de informe y presentación oral.</t>
-  </si>
-  <si>
-    <t>Se abordan gráficas trigonométricas y leyes de senos y cosenos, con hoja de trabajo y discusión grupal.</t>
-  </si>
-  <si>
     <t>Se analizan y grafican la parábola, la elipse y la hipérbola, con una hoja de trabajo como evidencia.</t>
-  </si>
-  <si>
-    <t>El proyecto final integra todos los contenidos del curso en una aplicación real, evaluado mediante exposición oral y entrega escrita.</t>
   </si>
   <si>
     <t>Prueba diagnóstica, hoja de repaso y dinámicas grupales, evaluadas mediante una lista de cotejo.</t>
@@ -313,7 +140,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,14 +159,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -546,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -590,21 +409,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -620,13 +424,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -648,14 +452,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -977,53 +784,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11FB33A-2EC9-4470-A975-E750206C5AD9}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
-    <col min="3" max="11" width="10.1796875" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="11" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="29"/>
-    </row>
-    <row r="2" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="34"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="30" t="s">
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="24"/>
+    </row>
+    <row r="2" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="29"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30" t="s">
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
       <c r="K2" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="3" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34"/>
-      <c r="B3" s="32"/>
+    <row r="3" spans="1:11" s="3" customFormat="1" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29"/>
+      <c r="B3" s="27"/>
       <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
@@ -1052,7 +859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>1</v>
       </c>
@@ -1069,7 +876,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>2</v>
       </c>
@@ -1086,7 +893,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>3</v>
       </c>
@@ -1103,7 +910,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>4</v>
       </c>
@@ -1120,7 +927,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>5</v>
       </c>
@@ -1137,7 +944,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>6</v>
       </c>
@@ -1154,7 +961,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>7</v>
       </c>
@@ -1171,7 +978,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>8</v>
       </c>
@@ -1188,7 +995,7 @@
       <c r="J11" s="4"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>9</v>
       </c>
@@ -1205,7 +1012,7 @@
       <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>10</v>
       </c>
@@ -1237,106 +1044,106 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75DA7F1-605D-4134-8590-05421821D0AF}">
   <dimension ref="B1:O14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.453125" customWidth="1"/>
-    <col min="3" max="3" width="46" style="27" customWidth="1"/>
-    <col min="4" max="15" width="7.1796875" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="46" style="22" customWidth="1"/>
+    <col min="4" max="15" width="7.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="20" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="33" t="s">
+    <row r="1" spans="2:15" ht="20.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="29"/>
-    </row>
-    <row r="3" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="34"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="30" t="s">
+      <c r="D2" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="24"/>
+    </row>
+    <row r="3" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="29"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30" t="s">
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="37"/>
-    </row>
-    <row r="4" spans="2:15" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="34"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="20">
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="32"/>
+    </row>
+    <row r="4" spans="2:15" s="3" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="29"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="15">
         <v>1</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="15">
         <v>2</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="15">
         <v>3</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="15">
         <v>4</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="15">
         <v>1</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="15">
         <v>2</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="15">
         <v>3</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="15">
         <v>4</v>
       </c>
-      <c r="L4" s="20">
+      <c r="L4" s="15">
         <v>1</v>
       </c>
-      <c r="M4" s="20">
+      <c r="M4" s="15">
         <v>2</v>
       </c>
-      <c r="N4" s="20">
+      <c r="N4" s="15">
         <v>3</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="18">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="13">
         <v>1</v>
       </c>
-      <c r="C5" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="22"/>
+      <c r="C5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="17"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -1349,15 +1156,15 @@
       <c r="N5" s="1"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="13">
         <v>2</v>
       </c>
-      <c r="C6" s="25" t="s">
-        <v>84</v>
+      <c r="C6" s="20" t="s">
+        <v>27</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="22"/>
+      <c r="E6" s="17"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1369,17 +1176,17 @@
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="13">
         <v>3</v>
       </c>
-      <c r="C7" s="25" t="s">
-        <v>85</v>
+      <c r="C7" s="20" t="s">
+        <v>28</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1389,18 +1196,18 @@
       <c r="N7" s="1"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13">
         <v>4</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>86</v>
+      <c r="C8" s="20" t="s">
+        <v>29</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="22"/>
+      <c r="H8" s="17"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1409,32 +1216,32 @@
       <c r="N8" s="1"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="13">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>92</v>
+      <c r="C9" s="20" t="s">
+        <v>35</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="13">
         <v>6</v>
       </c>
-      <c r="C10" s="25" t="s">
-        <v>87</v>
+      <c r="C10" s="20" t="s">
+        <v>30</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1443,18 +1250,18 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="22"/>
+      <c r="K10" s="17"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="2"/>
     </row>
-    <row r="11" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="13">
         <v>7</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>88</v>
+      <c r="C11" s="20" t="s">
+        <v>31</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1464,17 +1271,17 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="22"/>
+      <c r="L11" s="17"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13">
         <v>8</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>89</v>
+      <c r="C12" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1485,16 +1292,16 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="M12" s="22"/>
+      <c r="M12" s="17"/>
       <c r="N12" s="1"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13">
         <v>9</v>
       </c>
-      <c r="C13" s="25" t="s">
-        <v>81</v>
+      <c r="C13" s="20" t="s">
+        <v>25</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -1506,28 +1313,28 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="N13" s="22"/>
+      <c r="N13" s="33"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="2:15" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:15" ht="105" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="14">
         <v>10</v>
       </c>
-      <c r="C14" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="24"/>
+      <c r="C14" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1538,322 +1345,7 @@
     <mergeCell ref="L3:O3"/>
     <mergeCell ref="D2:O2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E23571D-7CFE-4DA0-8AF2-E5574AAB884F}">
-  <dimension ref="D5:I16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="5" spans="4:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="D5" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="4:9" ht="87" x14ac:dyDescent="0.35">
-      <c r="D6" s="15">
-        <v>1</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="4:9" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="D7" s="17">
-        <v>45718</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="19">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="8" spans="4:9" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="D8" s="17">
-        <v>45781</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="19">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="9" spans="4:9" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="D9" s="15">
-        <v>6</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="19">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="10" spans="4:9" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="D10" s="17">
-        <v>45876</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="19">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="11" spans="4:9" ht="116" x14ac:dyDescent="0.35">
-      <c r="D11" s="15">
-        <v>9</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="19">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="4:9" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="D12" s="15">
-        <v>10</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" s="19">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="4:9" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="D13" s="17">
-        <v>46002</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="19">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="14" spans="4:9" ht="87" x14ac:dyDescent="0.35">
-      <c r="D14" s="15">
-        <v>13</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" s="19">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="15" spans="4:9" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="D15" s="15">
-        <v>14</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="I15" s="19">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="16" spans="4:9" ht="58" x14ac:dyDescent="0.35">
-      <c r="D16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>71</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D483543-C16C-42CF-BC43-DD1A48771E7B}">
-  <dimension ref="E7:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="7" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>